--- a/results/optuna/optuna_alignment_experiment_tracker.xlsx
+++ b/results/optuna/optuna_alignment_experiment_tracker.xlsx
@@ -1795,7 +1795,7 @@
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="68" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[0.0, 0.1, 0.2]</t>
+          <t>[0.0, 0.1, 0.3]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>[128, 256]</t>
+          <t>[64, 128, 256]</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[0.0, 0.01]</t>
+          <t>[0.0, 0.3]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[3, 5]</t>
+          <t>[1, 3, 5]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>[1, 4]</t>
+          <t>[1, 2, 3]</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Optuna search choices</t>
+          <t>64: [1, 2]; 128: [1, 2]; 256: [1, 2]</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[24, 32, 48]</t>
+          <t>[32, 64, 128]</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
